--- a/app/src/main/java/com/example/methodmesh/modules/time_tools/docs/example_odk_time_tools.xlsx
+++ b/app/src/main/java/com/example/methodmesh/modules/time_tools/docs/example_odk_time_tools.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R671ba39bb9894fc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rf79d1fbeb15c466f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rffe8d4e104b94cf7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rb4b5132fdbe1470f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R26b7d8a2db6044d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R9f6285a4fb604e21"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3385,7 +3385,7 @@
         <x:v>field-list</x:v>
       </x:c>
       <x:c r="E142" s="2" t="str">
-        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='time.duration.calculate',input_a_ms=${input_a_ms},input_b_ms=${input_b_ms},input_operation=${input_operation},input_payload_mode='FULL',return_mode='flat')</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='time.duration.calculate',input_a_ms=${duration_a_input},input_b_ms=${duration_b_input},input_operation=${input_operation},input_payload_mode='FULL',return_mode='flat')</x:v>
       </x:c>
       <x:c r="F142" s="2" t="str"/>
       <x:c r="G142" s="2" t="str"/>
@@ -3400,7 +3400,7 @@
         <x:v>integer</x:v>
       </x:c>
       <x:c r="B143" s="2" t="str">
-        <x:v>input_a_ms</x:v>
+        <x:v>duration_a_input</x:v>
       </x:c>
       <x:c r="C143" s="2" t="str">
         <x:v>First duration (ms)</x:v>
@@ -3420,7 +3420,7 @@
         <x:v>integer</x:v>
       </x:c>
       <x:c r="B144" s="2" t="str">
-        <x:v>input_b_ms</x:v>
+        <x:v>duration_b_input</x:v>
       </x:c>
       <x:c r="C144" s="2" t="str">
         <x:v>Second duration (ms)</x:v>
@@ -3747,7 +3747,7 @@
         <x:v>methodmesh_time_tools_examples</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>2026090901</x:v>
+        <x:v>2026092201</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
